--- a/CodeSystem-mii-cs-pro-ssd-12-answers.xlsx
+++ b/CodeSystem-mii-cs-pro-ssd-12-answers.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc3</t>
+    <t>2027.0.0-ballot.rc4</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T17:47:08+00:00</t>
+    <t>2026-09-08T17:30:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -82,7 +82,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>MII-controlled frequency answer scale for SSD-12 (0-4). English display with German designation (original instrument wording). ordinalValue properties on each concept enable SDC ordinal scoring via answerValueSet.</t>
+    <t>MII-controlled frequency answer scale for SSD-12 (0-4). English display with German designation (original instrument wording). itemWeight properties on each concept enable SDC ordinal scoring via answerValueSet.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -130,13 +130,13 @@
     <t>Type</t>
   </si>
   <si>
-    <t>ordinalValue</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/ordinalValue</t>
-  </si>
-  <si>
-    <t>Numerical ordinal value (0-4) for SDC calculatedExpression scoring via .ordinal().sum()</t>
+    <t>itemWeight</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#itemWeight</t>
+  </si>
+  <si>
+    <t>Numerical ordinal value (0-4) for SDC calculatedExpression scoring via .weight().sum()</t>
   </si>
   <si>
     <t>decimal</t>

--- a/CodeSystem-mii-cs-pro-ssd-12-answers.xlsx
+++ b/CodeSystem-mii-cs-pro-ssd-12-answers.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc4</t>
+    <t>2027.0.0-ballot.rc5</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T17:30:22+00:00</t>
+    <t>2026-09-11T10:35:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-mii-cs-pro-ssd-12-answers.xlsx
+++ b/CodeSystem-mii-cs-pro-ssd-12-answers.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc5</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T10:35:27+00:00</t>
+    <t>2026-09-11T13:28:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-mii-cs-pro-ssd-12-answers.xlsx
+++ b/CodeSystem-mii-cs-pro-ssd-12-answers.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T13:28:57+00:00</t>
+    <t>2026-09-11T16:14:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
